--- a/full/sliding_window_results_window_8.xlsx
+++ b/full/sliding_window_results_window_8.xlsx
@@ -463,13 +463,13 @@
         <v>29.84</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29.88066855575936</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.84</v>
+        <v>0.04066855575935691</v>
       </c>
       <c r="E2" t="n">
-        <v>890.4256</v>
+        <v>0.001653931427551922</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.81</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29.77401489754656</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.81</v>
+        <v>-0.03598510245344144</v>
       </c>
       <c r="E3" t="n">
-        <v>888.6360999999999</v>
+        <v>0.001294927598584677</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>29.64367529096509</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.92</v>
+        <v>-0.2763247090349132</v>
       </c>
       <c r="E4" t="n">
-        <v>895.2064000000001</v>
+        <v>0.07635534482322946</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.9770110492835</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.98</v>
+        <v>-0.002988950716499517</v>
       </c>
       <c r="E5" t="n">
-        <v>898.8004000000001</v>
+        <v>8.933826385662973e-06</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.04</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>30.15190796648162</v>
       </c>
       <c r="D6" t="n">
-        <v>-30.04</v>
+        <v>0.1119079664816169</v>
       </c>
       <c r="E6" t="n">
-        <v>902.4015999999999</v>
+        <v>0.0125233929620507</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.21</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.34663417843318</v>
       </c>
       <c r="D7" t="n">
-        <v>-30.21</v>
+        <v>0.1366341784331802</v>
       </c>
       <c r="E7" t="n">
-        <v>912.6441000000001</v>
+        <v>0.01866889871611011</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.22</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.62369824705883</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.22</v>
+        <v>0.4036982470588342</v>
       </c>
       <c r="E8" t="n">
-        <v>913.2483999999999</v>
+        <v>0.1629722746783755</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.38</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.31539290832943</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.38</v>
+        <v>-0.06460709167056677</v>
       </c>
       <c r="E9" t="n">
-        <v>922.9444</v>
+        <v>0.004174076294129019</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.44</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.48004311243192</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.44</v>
+        <v>0.04004311243192049</v>
       </c>
       <c r="E10" t="n">
-        <v>926.5936</v>
+        <v>0.001603450853235425</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.48</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.62951007234524</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.48</v>
+        <v>0.1495100723452403</v>
       </c>
       <c r="E11" t="n">
-        <v>929.0304</v>
+        <v>0.02235326173267898</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.69</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.69147273849411</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.69</v>
+        <v>0.001472738494104675</v>
       </c>
       <c r="E12" t="n">
-        <v>941.8761000000001</v>
+        <v>2.168958672017706e-06</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.75</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.33463104955399</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.75</v>
+        <v>-0.415368950446009</v>
       </c>
       <c r="E13" t="n">
-        <v>945.5625</v>
+        <v>0.172531364994619</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.94</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>30.37174292734279</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.94</v>
+        <v>-0.5682570726572109</v>
       </c>
       <c r="E14" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3229161006249427</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.95</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.76360678343317</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.95</v>
+        <v>-0.1863932165668274</v>
       </c>
       <c r="E15" t="n">
-        <v>957.9024999999999</v>
+        <v>0.03474243118212822</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>31.06347961641817</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.02</v>
+        <v>0.04347961641817122</v>
       </c>
       <c r="E16" t="n">
-        <v>962.2404</v>
+        <v>0.001890477043871304</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.12</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>31.37022274551597</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.12</v>
+        <v>0.2502227455159662</v>
       </c>
       <c r="E17" t="n">
-        <v>968.4544000000001</v>
+        <v>0.062611422373548</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.28</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>31.36086790810678</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.28</v>
+        <v>0.08086790810678224</v>
       </c>
       <c r="E18" t="n">
-        <v>978.4384000000001</v>
+        <v>0.006539618561566977</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.38</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31.69297716748968</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.38</v>
+        <v>0.3129771674896844</v>
       </c>
       <c r="E19" t="n">
-        <v>984.7044</v>
+        <v>0.09795470736986596</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.58</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>32.00502054386315</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.58</v>
+        <v>0.4250205438631482</v>
       </c>
       <c r="E20" t="n">
-        <v>997.2963999999999</v>
+        <v>0.1806424627057263</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.65</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.95227342423743</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.65</v>
+        <v>0.302273424237427</v>
       </c>
       <c r="E21" t="n">
-        <v>1001.7225</v>
+        <v>0.0913692230002195</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.88</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.60719355010644</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.88</v>
+        <v>-0.2728064498935616</v>
       </c>
       <c r="E22" t="n">
-        <v>1016.3344</v>
+        <v>0.07442335910352835</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.28</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>32.13576646462457</v>
       </c>
       <c r="D23" t="n">
-        <v>-32.28</v>
+        <v>-0.1442335353754345</v>
       </c>
       <c r="E23" t="n">
-        <v>1041.9984</v>
+        <v>0.02080331272689671</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.45</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>32.14611717632918</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.45</v>
+        <v>-0.3038828236708184</v>
       </c>
       <c r="E24" t="n">
-        <v>1053.0025</v>
+        <v>0.09234477052214972</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.85</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>33.19851626968185</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.85</v>
+        <v>0.3485162696818449</v>
       </c>
       <c r="E25" t="n">
-        <v>1079.1225</v>
+        <v>0.1214635902329484</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>32.87005672226958</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.9</v>
+        <v>-0.02994327773041761</v>
       </c>
       <c r="E26" t="n">
-        <v>1082.41</v>
+        <v>0.0008965998812409229</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33.09926301179274</v>
       </c>
       <c r="D27" t="n">
-        <v>-33.1</v>
+        <v>-0.000736988207265199</v>
       </c>
       <c r="E27" t="n">
-        <v>1095.61</v>
+        <v>5.431516176479719e-07</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>33.11066246943691</v>
       </c>
       <c r="D28" t="n">
-        <v>-33.4</v>
+        <v>-0.2893375305630883</v>
       </c>
       <c r="E28" t="n">
-        <v>1115.56</v>
+        <v>0.08371620659234606</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.7</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>33.73068155870988</v>
       </c>
       <c r="D29" t="n">
-        <v>-33.7</v>
+        <v>0.03068155870987965</v>
       </c>
       <c r="E29" t="n">
-        <v>1135.69</v>
+        <v>0.000941358044867792</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>34.50721488327389</v>
       </c>
       <c r="D30" t="n">
-        <v>-34.1</v>
+        <v>0.4072148832738876</v>
       </c>
       <c r="E30" t="n">
-        <v>1162.81</v>
+        <v>0.1658239611597659</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.4</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>34.51580185188255</v>
       </c>
       <c r="D31" t="n">
-        <v>-34.4</v>
+        <v>0.1158018518825514</v>
       </c>
       <c r="E31" t="n">
-        <v>1183.36</v>
+        <v>0.01341006889942838</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.9</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>35.03799556991351</v>
       </c>
       <c r="D32" t="n">
-        <v>-34.9</v>
+        <v>0.1379955699135138</v>
       </c>
       <c r="E32" t="n">
-        <v>1218.01</v>
+        <v>0.01904277731575548</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.3</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>34.87663432728867</v>
       </c>
       <c r="D33" t="n">
-        <v>-35.3</v>
+        <v>-0.4233656727113271</v>
       </c>
       <c r="E33" t="n">
-        <v>1246.09</v>
+        <v>0.1792384928303145</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.7</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>35.17898363211293</v>
       </c>
       <c r="D34" t="n">
-        <v>-35.7</v>
+        <v>-0.5210163678870714</v>
       </c>
       <c r="E34" t="n">
-        <v>1274.49</v>
+        <v>0.2714580556062361</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.3</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>35.86378850647009</v>
       </c>
       <c r="D35" t="n">
-        <v>-36.3</v>
+        <v>-0.4362114935299033</v>
       </c>
       <c r="E35" t="n">
-        <v>1317.69</v>
+        <v>0.1902804670875889</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.8</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>36.26778913958069</v>
       </c>
       <c r="D36" t="n">
-        <v>-36.8</v>
+        <v>-0.5322108604193048</v>
       </c>
       <c r="E36" t="n">
-        <v>1354.24</v>
+        <v>0.2832483999482567</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.3</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>37.30114710264916</v>
       </c>
       <c r="D37" t="n">
-        <v>-37.3</v>
+        <v>0.001147102649163401</v>
       </c>
       <c r="E37" t="n">
-        <v>1391.29</v>
+        <v>1.315844487717692e-06</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.9</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>37.8392741502586</v>
       </c>
       <c r="D38" t="n">
-        <v>-37.9</v>
+        <v>-0.06072584974140227</v>
       </c>
       <c r="E38" t="n">
-        <v>1436.41</v>
+        <v>0.003687628826815366</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.5</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>38.43957258246311</v>
       </c>
       <c r="D39" t="n">
-        <v>-38.5</v>
+        <v>-0.06042741753689285</v>
       </c>
       <c r="E39" t="n">
-        <v>1482.25</v>
+        <v>0.003651472790177985</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.9</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>39.34244782130198</v>
       </c>
       <c r="D40" t="n">
-        <v>-38.9</v>
+        <v>0.4424478213019825</v>
       </c>
       <c r="E40" t="n">
-        <v>1513.21</v>
+        <v>0.195760074574871</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.4</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>40.07310150521455</v>
       </c>
       <c r="D41" t="n">
-        <v>-39.4</v>
+        <v>0.6731015052145466</v>
       </c>
       <c r="E41" t="n">
-        <v>1552.36</v>
+        <v>0.4530656363220883</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.9</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>40.34373512892738</v>
       </c>
       <c r="D42" t="n">
-        <v>-39.9</v>
+        <v>0.4437351289273792</v>
       </c>
       <c r="E42" t="n">
-        <v>1592.01</v>
+        <v>0.1969008646441978</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.1</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>40.02935357895179</v>
       </c>
       <c r="D43" t="n">
-        <v>-40.1</v>
+        <v>-0.07064642104820962</v>
       </c>
       <c r="E43" t="n">
-        <v>1608.01</v>
+        <v>0.004990916806920915</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.6</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>41.19614329238238</v>
       </c>
       <c r="D44" t="n">
-        <v>-40.6</v>
+        <v>0.5961432923823793</v>
       </c>
       <c r="E44" t="n">
-        <v>1648.36</v>
+        <v>0.355386825052503</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.9</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>41.43468154294521</v>
       </c>
       <c r="D45" t="n">
-        <v>-40.9</v>
+        <v>0.534681542945215</v>
       </c>
       <c r="E45" t="n">
-        <v>1672.81</v>
+        <v>0.2858843523662757</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.2</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>41.23756675007412</v>
       </c>
       <c r="D46" t="n">
-        <v>-41.2</v>
+        <v>0.03756675007411303</v>
       </c>
       <c r="E46" t="n">
-        <v>1697.44</v>
+        <v>0.001411260711130871</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.5</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>41.01664378554329</v>
       </c>
       <c r="D47" t="n">
-        <v>-41.5</v>
+        <v>-0.4833562144567125</v>
       </c>
       <c r="E47" t="n">
-        <v>1722.25</v>
+        <v>0.2336332300539234</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.8</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>41.4105672201997</v>
       </c>
       <c r="D48" t="n">
-        <v>-41.8</v>
+        <v>-0.3894327798002948</v>
       </c>
       <c r="E48" t="n">
-        <v>1747.24</v>
+        <v>0.1516578899829849</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>41.92653814877664</v>
       </c>
       <c r="D49" t="n">
-        <v>-42.2</v>
+        <v>-0.2734618512233666</v>
       </c>
       <c r="E49" t="n">
-        <v>1780.84</v>
+        <v>0.07478138407451071</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.7</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>42.23666827446134</v>
       </c>
       <c r="D50" t="n">
-        <v>-42.7</v>
+        <v>-0.4633317255386586</v>
       </c>
       <c r="E50" t="n">
-        <v>1823.29</v>
+        <v>0.2146762878906309</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>43.7</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>43.37985615845385</v>
       </c>
       <c r="D51" t="n">
-        <v>-43.7</v>
+        <v>-0.3201438415461553</v>
       </c>
       <c r="E51" t="n">
-        <v>1909.69</v>
+        <v>0.1024920792799298</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1729.34</v>
+        <v>-0.5573866408334638</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>60729.29000000001</v>
+        <v>5.067881652051883</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1214.5858</v>
+        <v>0.1013576330410376</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_8.xlsx
+++ b/full/sliding_window_results_window_8.xlsx
@@ -463,13 +463,13 @@
         <v>29.84</v>
       </c>
       <c r="C2" t="n">
-        <v>29.88066855575936</v>
+        <v>29.84835671807618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04066855575935691</v>
+        <v>0.008356718076182545</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001653931427551922</v>
+        <v>6.983473700479611e-05</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.81</v>
       </c>
       <c r="C3" t="n">
-        <v>29.77401489754656</v>
+        <v>29.6853234929752</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03598510245344144</v>
+        <v>-0.1246765070248017</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001294927598584677</v>
+        <v>0.01554423140390543</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>29.64367529096509</v>
+        <v>29.75264016708576</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2763247090349132</v>
+        <v>-0.1673598329142401</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07635534482322946</v>
+        <v>0.02800931367308235</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.98</v>
       </c>
       <c r="C5" t="n">
-        <v>29.9770110492835</v>
+        <v>29.94321390172189</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002988950716499517</v>
+        <v>-0.03678609827810675</v>
       </c>
       <c r="E5" t="n">
-        <v>8.933826385662973e-06</v>
+        <v>0.001353217026526528</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.04</v>
       </c>
       <c r="C6" t="n">
-        <v>30.15190796648162</v>
+        <v>30.0791490409676</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1119079664816169</v>
+        <v>0.03914904096760097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0125233929620507</v>
+        <v>0.001532647408682899</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.21</v>
       </c>
       <c r="C7" t="n">
-        <v>30.34663417843318</v>
+        <v>29.94070693723334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1366341784331802</v>
+        <v>-0.269293062766657</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01866889871611011</v>
+        <v>0.07251875365424666</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.22</v>
       </c>
       <c r="C8" t="n">
-        <v>30.62369824705883</v>
+        <v>30.0128498594681</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4036982470588342</v>
+        <v>-0.2071501405318941</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1629722746783755</v>
+        <v>0.04291118072238346</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.38</v>
       </c>
       <c r="C9" t="n">
-        <v>30.31539290832943</v>
+        <v>30.0965275628737</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06460709167056677</v>
+        <v>-0.2834724371262958</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004174076294129019</v>
+        <v>0.08035662261032171</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.44</v>
       </c>
       <c r="C10" t="n">
-        <v>30.48004311243192</v>
+        <v>30.18238374103743</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04004311243192049</v>
+        <v>-0.2576162589625675</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001603450853235425</v>
+        <v>0.06636613688186861</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.48</v>
       </c>
       <c r="C11" t="n">
-        <v>30.62951007234524</v>
+        <v>30.42338070205161</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1495100723452403</v>
+        <v>-0.05661929794839082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02235326173267898</v>
+        <v>0.003205744900168653</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.69</v>
       </c>
       <c r="C12" t="n">
-        <v>30.69147273849411</v>
+        <v>30.62601754640027</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001472738494104675</v>
+        <v>-0.06398245359972776</v>
       </c>
       <c r="E12" t="n">
-        <v>2.168958672017706e-06</v>
+        <v>0.004093754368641316</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.75</v>
       </c>
       <c r="C13" t="n">
-        <v>30.33463104955399</v>
+        <v>30.31273411101651</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.415368950446009</v>
+        <v>-0.437265888983486</v>
       </c>
       <c r="E13" t="n">
-        <v>0.172531364994619</v>
+        <v>0.1912014576685183</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.94</v>
       </c>
       <c r="C14" t="n">
-        <v>30.37174292734279</v>
+        <v>30.63782043116669</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5682570726572109</v>
+        <v>-0.3021795688333064</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3229161006249427</v>
+        <v>0.09131249182028298</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.95</v>
       </c>
       <c r="C15" t="n">
-        <v>30.76360678343317</v>
+        <v>30.76783400388231</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1863932165668274</v>
+        <v>-0.1821659961176927</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03474243118212822</v>
+        <v>0.03318445014155123</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.02</v>
       </c>
       <c r="C16" t="n">
-        <v>31.06347961641817</v>
+        <v>30.99338847788218</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04347961641817122</v>
+        <v>-0.02661152211781825</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001890477043871304</v>
+        <v>0.0007081731094271301</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.12</v>
       </c>
       <c r="C17" t="n">
-        <v>31.37022274551597</v>
+        <v>31.14833754246468</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2502227455159662</v>
+        <v>0.0283375424646799</v>
       </c>
       <c r="E17" t="n">
-        <v>0.062611422373548</v>
+        <v>0.0008030163129375365</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.28</v>
       </c>
       <c r="C18" t="n">
-        <v>31.36086790810678</v>
+        <v>31.27862360332534</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08086790810678224</v>
+        <v>-0.001376396674665159</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006539618561566977</v>
+        <v>1.894467806029308e-06</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.38</v>
       </c>
       <c r="C19" t="n">
-        <v>31.69297716748968</v>
+        <v>31.37579292180769</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3129771674896844</v>
+        <v>-0.004207078192312252</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09795470736986596</v>
+        <v>1.769950691622933e-05</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.58</v>
       </c>
       <c r="C20" t="n">
-        <v>32.00502054386315</v>
+        <v>31.57238161477221</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4250205438631482</v>
+        <v>-0.007618385227786462</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1806424627057263</v>
+        <v>5.803979347895498e-05</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.65</v>
       </c>
       <c r="C21" t="n">
-        <v>31.95227342423743</v>
+        <v>31.50157555459989</v>
       </c>
       <c r="D21" t="n">
-        <v>0.302273424237427</v>
+        <v>-0.1484244454001065</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0913692230002195</v>
+        <v>0.02202981599232919</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.88</v>
       </c>
       <c r="C22" t="n">
-        <v>31.60719355010644</v>
+        <v>31.74472873825188</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2728064498935616</v>
+        <v>-0.1352712617481195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07442335910352835</v>
+        <v>0.01829831425492827</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.28</v>
       </c>
       <c r="C23" t="n">
-        <v>32.13576646462457</v>
+        <v>32.05056031788173</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1442335353754345</v>
+        <v>-0.2294396821182687</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02080331272689671</v>
+        <v>0.05264256773053219</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.45</v>
       </c>
       <c r="C24" t="n">
-        <v>32.14611717632918</v>
+        <v>32.06806518986735</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3038828236708184</v>
+        <v>-0.3819348101326554</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09234477052214972</v>
+        <v>0.1458741991910675</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.85</v>
       </c>
       <c r="C25" t="n">
-        <v>33.19851626968185</v>
+        <v>33.06392065491861</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3485162696818449</v>
+        <v>0.2139206549186099</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1214635902329484</v>
+        <v>0.04576204660080697</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.9</v>
       </c>
       <c r="C26" t="n">
-        <v>32.87005672226958</v>
+        <v>32.75376778877107</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.02994327773041761</v>
+        <v>-0.1462322112289272</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0008965998812409229</v>
+        <v>0.02138385960090157</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.1</v>
       </c>
       <c r="C27" t="n">
-        <v>33.09926301179274</v>
+        <v>33.02194232137766</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.000736988207265199</v>
+        <v>-0.07805767862234347</v>
       </c>
       <c r="E27" t="n">
-        <v>5.431516176479719e-07</v>
+        <v>0.006093001191909057</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.4</v>
       </c>
       <c r="C28" t="n">
-        <v>33.11066246943691</v>
+        <v>33.15839041642171</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2893375305630883</v>
+        <v>-0.2416095835782883</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08371620659234606</v>
+        <v>0.05837519087687389</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.7</v>
       </c>
       <c r="C29" t="n">
-        <v>33.73068155870988</v>
+        <v>33.56309354778768</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03068155870987965</v>
+        <v>-0.1369064522123224</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000941358044867792</v>
+        <v>0.01874337665736493</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.1</v>
       </c>
       <c r="C30" t="n">
-        <v>34.50721488327389</v>
+        <v>34.10119175165288</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4072148832738876</v>
+        <v>0.001191751652875439</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1658239611597659</v>
+        <v>1.420272002131341e-06</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.4</v>
       </c>
       <c r="C31" t="n">
-        <v>34.51580185188255</v>
+        <v>34.21909919526377</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1158018518825514</v>
+        <v>-0.1809008047362326</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01341006889942838</v>
+        <v>0.03272510115421656</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.9</v>
       </c>
       <c r="C32" t="n">
-        <v>35.03799556991351</v>
+        <v>34.99496461507115</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1379955699135138</v>
+        <v>0.09496461507115583</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01904277731575548</v>
+        <v>0.009018278115612798</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>35.3</v>
       </c>
       <c r="C33" t="n">
-        <v>34.87663432728867</v>
+        <v>34.85139858376304</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4233656727113271</v>
+        <v>-0.4486014162369614</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1792384928303145</v>
+        <v>0.2012432306498075</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.7</v>
       </c>
       <c r="C34" t="n">
-        <v>35.17898363211293</v>
+        <v>35.33429359960448</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5210163678870714</v>
+        <v>-0.3657064003955242</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2714580556062361</v>
+        <v>0.1337411712902514</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>36.3</v>
       </c>
       <c r="C35" t="n">
-        <v>35.86378850647009</v>
+        <v>36.14838327858308</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4362114935299033</v>
+        <v>-0.1516167214169215</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1902804670875889</v>
+        <v>0.02298763021321638</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.8</v>
       </c>
       <c r="C36" t="n">
-        <v>36.26778913958069</v>
+        <v>36.59456942887319</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5322108604193048</v>
+        <v>-0.2054305711268114</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2832483999482567</v>
+        <v>0.04220171955348792</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>37.3</v>
       </c>
       <c r="C37" t="n">
-        <v>37.30114710264916</v>
+        <v>37.25191942401533</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001147102649163401</v>
+        <v>-0.0480805759846632</v>
       </c>
       <c r="E37" t="n">
-        <v>1.315844487717692e-06</v>
+        <v>0.002311741787016972</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.9</v>
       </c>
       <c r="C38" t="n">
-        <v>37.8392741502586</v>
+        <v>37.85365036555459</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.06072584974140227</v>
+        <v>-0.04634963444541285</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003687628826815366</v>
+        <v>0.002148288613223401</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>38.5</v>
       </c>
       <c r="C39" t="n">
-        <v>38.43957258246311</v>
+        <v>38.25037326682311</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.06042741753689285</v>
+        <v>-0.2496267331768891</v>
       </c>
       <c r="E39" t="n">
-        <v>0.003651472790177985</v>
+        <v>0.06231350591656579</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.9</v>
       </c>
       <c r="C40" t="n">
-        <v>39.34244782130198</v>
+        <v>38.64874197058322</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4424478213019825</v>
+        <v>-0.2512580294167819</v>
       </c>
       <c r="E40" t="n">
-        <v>0.195760074574871</v>
+        <v>0.06313059734640443</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>39.4</v>
       </c>
       <c r="C41" t="n">
-        <v>40.07310150521455</v>
+        <v>39.20737969592765</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6731015052145466</v>
+        <v>-0.1926203040723493</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4530656363220883</v>
+        <v>0.03710258154092431</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.9</v>
       </c>
       <c r="C42" t="n">
-        <v>40.34373512892738</v>
+        <v>39.55080939093362</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4437351289273792</v>
+        <v>-0.3491906090663761</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1969008646441978</v>
+        <v>0.1219340814601467</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.1</v>
       </c>
       <c r="C43" t="n">
-        <v>40.02935357895179</v>
+        <v>40.25730006692402</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.07064642104820962</v>
+        <v>0.1573000669240159</v>
       </c>
       <c r="E43" t="n">
-        <v>0.004990916806920915</v>
+        <v>0.02474331105429987</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.6</v>
       </c>
       <c r="C44" t="n">
-        <v>41.19614329238238</v>
+        <v>40.46743440074381</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5961432923823793</v>
+        <v>-0.1325655992561963</v>
       </c>
       <c r="E44" t="n">
-        <v>0.355386825052503</v>
+        <v>0.01757363810615442</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.9</v>
       </c>
       <c r="C45" t="n">
-        <v>41.43468154294521</v>
+        <v>40.96963270943314</v>
       </c>
       <c r="D45" t="n">
-        <v>0.534681542945215</v>
+        <v>0.0696327094331437</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2858843523662757</v>
+        <v>0.00484871422300062</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.2</v>
       </c>
       <c r="C46" t="n">
-        <v>41.23756675007412</v>
+        <v>41.41944056782867</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03756675007411303</v>
+        <v>0.2194405678286628</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001411260711130871</v>
+        <v>0.04815416280896598</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.5</v>
       </c>
       <c r="C47" t="n">
-        <v>41.01664378554329</v>
+        <v>41.18069323978725</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4833562144567125</v>
+        <v>-0.3193067602127542</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2336332300539234</v>
+        <v>0.1019568071175653</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.8</v>
       </c>
       <c r="C48" t="n">
-        <v>41.4105672201997</v>
+        <v>41.46773964005158</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3894327798002948</v>
+        <v>-0.3322603599484211</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1516578899829849</v>
+        <v>0.1103969467930543</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>42.2</v>
       </c>
       <c r="C49" t="n">
-        <v>41.92653814877664</v>
+        <v>41.84603757489475</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2734618512233666</v>
+        <v>-0.3539624251052516</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07478138407451071</v>
+        <v>0.1252893983863908</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.7</v>
       </c>
       <c r="C50" t="n">
-        <v>42.23666827446134</v>
+        <v>42.49977497925924</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4633317255386586</v>
+        <v>-0.2002250207407599</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2146762878906309</v>
+        <v>0.04009005893063772</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>43.7</v>
       </c>
       <c r="C51" t="n">
-        <v>43.37985615845385</v>
+        <v>43.58293194512007</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3201438415461553</v>
+        <v>-0.1170680548799297</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1024920792799298</v>
+        <v>0.01370492947337022</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.5573866408334638</v>
+        <v>-7.038733403222089</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>5.067881652051883</v>
+        <v>2.24006834711078</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1013576330410376</v>
+        <v>0.0448013669422156</v>
       </c>
     </row>
   </sheetData>
